--- a/Data/BaseData/df_kpi_annuities.xlsx
+++ b/Data/BaseData/df_kpi_annuities.xlsx
@@ -359,7 +359,7 @@
         <v>1949</v>
       </c>
       <c r="B2" t="n">
-        <v>5.1</v>
+        <v>1.051</v>
       </c>
     </row>
     <row r="3">
@@ -367,7 +367,7 @@
         <v>1950</v>
       </c>
       <c r="B3" t="n">
-        <v>5.3</v>
+        <v>1.106703</v>
       </c>
     </row>
     <row r="4">
@@ -375,7 +375,7 @@
         <v>1951</v>
       </c>
       <c r="B4" t="n">
-        <v>6.2</v>
+        <v>1.175318586</v>
       </c>
     </row>
     <row r="5">
@@ -383,7 +383,7 @@
         <v>1952</v>
       </c>
       <c r="B5" t="n">
-        <v>6.7</v>
+        <v>1.254064931262</v>
       </c>
     </row>
     <row r="6">
@@ -391,7 +391,7 @@
         <v>1953</v>
       </c>
       <c r="B6" t="n">
-        <v>6.9</v>
+        <v>1.34059541151908</v>
       </c>
     </row>
     <row r="7">
@@ -399,7 +399,7 @@
         <v>1954</v>
       </c>
       <c r="B7" t="n">
-        <v>7.1</v>
+        <v>1.43577768573693</v>
       </c>
     </row>
     <row r="8">
@@ -407,7 +407,7 @@
         <v>1955</v>
       </c>
       <c r="B8" t="n">
-        <v>7.2</v>
+        <v>1.53915367910999</v>
       </c>
     </row>
     <row r="9">
@@ -415,7 +415,7 @@
         <v>1956</v>
       </c>
       <c r="B9" t="n">
-        <v>7.5</v>
+        <v>1.65459020504324</v>
       </c>
     </row>
     <row r="10">
@@ -423,7 +423,7 @@
         <v>1957</v>
       </c>
       <c r="B10" t="n">
-        <v>7.7</v>
+        <v>1.78199365083157</v>
       </c>
     </row>
     <row r="11">
@@ -431,7 +431,7 @@
         <v>1958</v>
       </c>
       <c r="B11" t="n">
-        <v>8.1</v>
+        <v>1.92633513654893</v>
       </c>
     </row>
     <row r="12">
@@ -439,7 +439,7 @@
         <v>1959</v>
       </c>
       <c r="B12" t="n">
-        <v>8.3</v>
+        <v>2.08622095288249</v>
       </c>
     </row>
     <row r="13">
@@ -447,7 +447,7 @@
         <v>1960</v>
       </c>
       <c r="B13" t="n">
-        <v>8.3</v>
+        <v>2.25937729197173</v>
       </c>
     </row>
     <row r="14">
@@ -455,7 +455,7 @@
         <v>1961</v>
       </c>
       <c r="B14" t="n">
-        <v>8.5</v>
+        <v>2.45142436178933</v>
       </c>
     </row>
     <row r="15">
@@ -463,7 +463,7 @@
         <v>1962</v>
       </c>
       <c r="B15" t="n">
-        <v>8.9</v>
+        <v>2.66960112998858</v>
       </c>
     </row>
     <row r="16">
@@ -471,7 +471,7 @@
         <v>1963</v>
       </c>
       <c r="B16" t="n">
-        <v>9.2</v>
+        <v>2.91520443394753</v>
       </c>
     </row>
     <row r="17">
@@ -479,7 +479,7 @@
         <v>1964</v>
       </c>
       <c r="B17" t="n">
-        <v>9.7</v>
+        <v>3.19797926404044</v>
       </c>
     </row>
     <row r="18">
@@ -487,7 +487,7 @@
         <v>1965</v>
       </c>
       <c r="B18" t="n">
-        <v>10.1</v>
+        <v>3.52097516970853</v>
       </c>
     </row>
     <row r="19">
@@ -495,7 +495,7 @@
         <v>1966</v>
       </c>
       <c r="B19" t="n">
-        <v>10.4</v>
+        <v>3.88715658735821</v>
       </c>
     </row>
     <row r="20">
@@ -503,7 +503,7 @@
         <v>1967</v>
       </c>
       <c r="B20" t="n">
-        <v>10.9</v>
+        <v>4.31085665538026</v>
       </c>
     </row>
     <row r="21">
@@ -511,7 +511,7 @@
         <v>1968</v>
       </c>
       <c r="B21" t="n">
-        <v>11.3</v>
+        <v>4.79798345743823</v>
       </c>
     </row>
     <row r="22">
@@ -519,7 +519,7 @@
         <v>1969</v>
       </c>
       <c r="B22" t="n">
-        <v>11.6</v>
+        <v>5.35454953850106</v>
       </c>
     </row>
     <row r="23">
@@ -527,7 +527,7 @@
         <v>1970</v>
       </c>
       <c r="B23" t="n">
-        <v>12.8</v>
+        <v>6.0399318794292</v>
       </c>
     </row>
     <row r="24">
@@ -535,7 +535,7 @@
         <v>1971</v>
       </c>
       <c r="B24" t="n">
-        <v>6.1</v>
+        <v>6.40836772407438</v>
       </c>
     </row>
     <row r="25">
@@ -543,7 +543,7 @@
         <v>1972</v>
       </c>
       <c r="B25" t="n">
-        <v>4.8</v>
+        <v>6.71596937482995</v>
       </c>
     </row>
     <row r="26">
@@ -551,7 +551,7 @@
         <v>1973</v>
       </c>
       <c r="B26" t="n">
-        <v>6.4</v>
+        <v>7.14579141481907</v>
       </c>
     </row>
     <row r="27">
@@ -559,7 +559,7 @@
         <v>1974</v>
       </c>
       <c r="B27" t="n">
-        <v>16.5</v>
+        <v>8.32484699826422</v>
       </c>
     </row>
     <row r="28">
@@ -567,7 +567,7 @@
         <v>1975</v>
       </c>
       <c r="B28" t="n">
-        <v>9.9</v>
+        <v>9.14900685109238</v>
       </c>
     </row>
     <row r="29">
@@ -575,7 +575,7 @@
         <v>1976</v>
       </c>
       <c r="B29" t="n">
-        <v>9.4</v>
+        <v>10.0090134950951</v>
       </c>
     </row>
     <row r="30">
@@ -583,7 +583,7 @@
         <v>1977</v>
       </c>
       <c r="B30" t="n">
-        <v>8.5</v>
+        <v>10.8597796421781</v>
       </c>
     </row>
     <row r="31">
@@ -591,7 +591,7 @@
         <v>1978</v>
       </c>
       <c r="B31" t="n">
-        <v>3.5</v>
+        <v>11.2398719296544</v>
       </c>
     </row>
     <row r="32">
@@ -599,7 +599,7 @@
         <v>1979</v>
       </c>
       <c r="B32" t="n">
-        <v>5.6</v>
+        <v>11.869304757715</v>
       </c>
     </row>
     <row r="33">
@@ -607,7 +607,7 @@
         <v>1980</v>
       </c>
       <c r="B33" t="n">
-        <v>11.6</v>
+        <v>13.24614410961</v>
       </c>
     </row>
     <row r="34">
@@ -615,7 +615,7 @@
         <v>1981</v>
       </c>
       <c r="B34" t="n">
-        <v>8.8</v>
+        <v>14.4118047912556</v>
       </c>
     </row>
     <row r="35">
@@ -623,7 +623,7 @@
         <v>1982</v>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>15.7088672224686</v>
       </c>
     </row>
     <row r="36">
@@ -631,7 +631,7 @@
         <v>1983</v>
       </c>
       <c r="B36" t="n">
-        <v>8.1</v>
+        <v>16.9812854674886</v>
       </c>
     </row>
     <row r="37">
@@ -639,7 +639,7 @@
         <v>1984</v>
       </c>
       <c r="B37" t="n">
-        <v>6.6</v>
+        <v>18.1020503083429</v>
       </c>
     </row>
     <row r="38">
@@ -647,7 +647,7 @@
         <v>1985</v>
       </c>
       <c r="B38" t="n">
-        <v>4.3</v>
+        <v>18.8804384716016</v>
       </c>
     </row>
     <row r="39">
@@ -655,7 +655,7 @@
         <v>1986</v>
       </c>
       <c r="B39" t="n">
-        <v>7.1</v>
+        <v>20.2209496030853</v>
       </c>
     </row>
     <row r="40">
@@ -663,7 +663,7 @@
         <v>1987</v>
       </c>
       <c r="B40" t="n">
-        <v>9.1</v>
+        <v>22.0610560169661</v>
       </c>
     </row>
     <row r="41">
@@ -671,7 +671,7 @@
         <v>1988</v>
       </c>
       <c r="B41" t="n">
-        <v>4.9</v>
+        <v>23.1420477617974</v>
       </c>
     </row>
     <row r="42">
@@ -679,7 +679,7 @@
         <v>1989</v>
       </c>
       <c r="B42" t="n">
-        <v>0.7</v>
+        <v>23.30404209613</v>
       </c>
     </row>
     <row r="43">
@@ -687,7 +687,7 @@
         <v>1990</v>
       </c>
       <c r="B43" t="n">
-        <v>-1.5</v>
+        <v>22.954481464688</v>
       </c>
     </row>
     <row r="44">
@@ -695,7 +695,7 @@
         <v>1991</v>
       </c>
       <c r="B44" t="n">
-        <v>0.5</v>
+        <v>23.0692538720115</v>
       </c>
     </row>
     <row r="45">
@@ -703,7 +703,7 @@
         <v>1992</v>
       </c>
       <c r="B45" t="n">
-        <v>-0.7</v>
+        <v>22.9077690949074</v>
       </c>
     </row>
     <row r="46">
@@ -711,7 +711,7 @@
         <v>1993</v>
       </c>
       <c r="B46" t="n">
-        <v>0.4</v>
+        <v>22.999400171287</v>
       </c>
     </row>
     <row r="47">
@@ -719,7 +719,7 @@
         <v>1994</v>
       </c>
       <c r="B47" t="n">
-        <v>2.6</v>
+        <v>23.5973845757405</v>
       </c>
     </row>
     <row r="48">
@@ -727,7 +727,7 @@
         <v>1995</v>
       </c>
       <c r="B48" t="n">
-        <v>2.3</v>
+        <v>24.1401244209825</v>
       </c>
     </row>
     <row r="49">
@@ -735,7 +735,7 @@
         <v>1996</v>
       </c>
       <c r="B49" t="n">
-        <v>-0.3</v>
+        <v>24.0677040477196</v>
       </c>
     </row>
     <row r="50">
@@ -743,7 +743,7 @@
         <v>1997</v>
       </c>
       <c r="B50" t="n">
-        <v>0.2</v>
+        <v>24.115839455815</v>
       </c>
     </row>
     <row r="51">
@@ -751,7 +751,7 @@
         <v>1998</v>
       </c>
       <c r="B51" t="n">
-        <v>3.2</v>
+        <v>24.8875463184011</v>
       </c>
     </row>
     <row r="52">
@@ -759,7 +759,7 @@
         <v>1999</v>
       </c>
       <c r="B52" t="n">
-        <v>1.6</v>
+        <v>25.2857470594955</v>
       </c>
     </row>
     <row r="53">
@@ -767,7 +767,7 @@
         <v>2000</v>
       </c>
       <c r="B53" t="n">
-        <v>2.8</v>
+        <v>25.9937479771614</v>
       </c>
     </row>
     <row r="54">
@@ -775,7 +775,7 @@
         <v>2001</v>
       </c>
       <c r="B54" t="n">
-        <v>4.2</v>
+        <v>27.0854853922022</v>
       </c>
     </row>
     <row r="55">
@@ -783,7 +783,7 @@
         <v>2002</v>
       </c>
       <c r="B55" t="n">
-        <v>-0.8</v>
+        <v>26.8688015090645</v>
       </c>
     </row>
     <row r="56">
@@ -791,7 +791,7 @@
         <v>2003</v>
       </c>
       <c r="B56" t="n">
-        <v>-1.7</v>
+        <v>26.4120318834104</v>
       </c>
     </row>
     <row r="57">
@@ -799,7 +799,7 @@
         <v>2004</v>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>27.4685131587469</v>
       </c>
     </row>
     <row r="58">
@@ -807,7 +807,7 @@
         <v>2005</v>
       </c>
       <c r="B58" t="n">
-        <v>3.1</v>
+        <v>28.320037066668</v>
       </c>
     </row>
     <row r="59">
@@ -815,7 +815,7 @@
         <v>2006</v>
       </c>
       <c r="B59" t="n">
-        <v>4.1</v>
+        <v>29.4811585864014</v>
       </c>
     </row>
     <row r="60">
@@ -823,7 +823,7 @@
         <v>2007</v>
       </c>
       <c r="B60" t="n">
-        <v>5.7</v>
+        <v>31.1615846258263</v>
       </c>
     </row>
     <row r="61">
@@ -831,7 +831,7 @@
         <v>2008</v>
       </c>
       <c r="B61" t="n">
-        <v>5.6</v>
+        <v>32.9066333648726</v>
       </c>
     </row>
     <row r="62">
@@ -839,7 +839,7 @@
         <v>2009</v>
       </c>
       <c r="B62" t="n">
-        <v>1.6</v>
+        <v>33.4331394987105</v>
       </c>
     </row>
     <row r="63">
@@ -847,7 +847,7 @@
         <v>2010</v>
       </c>
       <c r="B63" t="n">
-        <v>-0.7</v>
+        <v>33.1991075222195</v>
       </c>
     </row>
     <row r="64">
@@ -855,7 +855,7 @@
         <v>2011</v>
       </c>
       <c r="B64" t="n">
-        <v>3.5</v>
+        <v>34.3610762854972</v>
       </c>
     </row>
     <row r="65">
@@ -863,7 +863,7 @@
         <v>2012</v>
       </c>
       <c r="B65" t="n">
-        <v>2.5</v>
+        <v>35.2201031926346</v>
       </c>
     </row>
     <row r="66">
@@ -871,7 +871,7 @@
         <v>2013</v>
       </c>
       <c r="B66" t="n">
-        <v>-1.1</v>
+        <v>34.8326820575157</v>
       </c>
     </row>
     <row r="67">
@@ -879,7 +879,7 @@
         <v>2014</v>
       </c>
       <c r="B67" t="n">
-        <v>2.9</v>
+        <v>35.8428298371836</v>
       </c>
     </row>
     <row r="68">
@@ -887,7 +887,7 @@
         <v>2015</v>
       </c>
       <c r="B68" t="n">
-        <v>4.3</v>
+        <v>37.3840715201825</v>
       </c>
     </row>
     <row r="69">
@@ -895,7 +895,7 @@
         <v>2016</v>
       </c>
       <c r="B69" t="n">
-        <v>2.5</v>
+        <v>38.3186733081871</v>
       </c>
     </row>
     <row r="70">
@@ -903,7 +903,7 @@
         <v>2017</v>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>39.0850467743508</v>
       </c>
     </row>
     <row r="71">
@@ -911,7 +911,7 @@
         <v>2018</v>
       </c>
       <c r="B71" t="n">
-        <v>2.6</v>
+        <v>40.1012579904839</v>
       </c>
     </row>
     <row r="72">
@@ -919,7 +919,7 @@
         <v>2019</v>
       </c>
       <c r="B72" t="n">
-        <v>2.7</v>
+        <v>41.183991956227</v>
       </c>
     </row>
     <row r="73">
@@ -927,7 +927,7 @@
         <v>2020</v>
       </c>
       <c r="B73" t="n">
-        <v>6.8</v>
+        <v>43.9845034092504</v>
       </c>
     </row>
     <row r="74">
@@ -935,7 +935,7 @@
         <v>2021</v>
       </c>
       <c r="B74" t="n">
-        <v>3.4</v>
+        <v>45.479976525165</v>
       </c>
     </row>
     <row r="75">
@@ -943,7 +943,7 @@
         <v>2022</v>
       </c>
       <c r="B75" t="n">
-        <v>9.4</v>
+        <v>49.7550943185305</v>
       </c>
     </row>
     <row r="76">
@@ -951,7 +951,7 @@
         <v>2023</v>
       </c>
       <c r="B76" t="n">
-        <v>7.4</v>
+        <v>53.4369712981017</v>
       </c>
     </row>
     <row r="77">
@@ -959,7 +959,7 @@
         <v>2024</v>
       </c>
       <c r="B77" t="n">
-        <v>4.4</v>
+        <v>55.7881980352182</v>
       </c>
     </row>
     <row r="78">
@@ -967,7 +967,7 @@
         <v>2025</v>
       </c>
       <c r="B78" t="n">
-        <v>3.2</v>
+        <v>57.5734203723452</v>
       </c>
     </row>
   </sheetData>
